--- a/reports/ai_readiness_2026-W26.xlsx
+++ b/reports/ai_readiness_2026-W26.xlsx
@@ -440,7 +440,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:07 UTC</t>
+          <t>Generated: 2026-06-22 17:48 UTC</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LifeEcho (85)</t>
+          <t>Listn (85)</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.8</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="7">
@@ -778,30 +778,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Timeout</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="n">
-        <v>100</v>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1038,7 +1044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:07 UTC</t>
+          <t>Generated: 2026-06-22 17:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1171,10 +1177,10 @@
         <v>85</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="12">
